--- a/publication_tables/supplementary/S10_macro_results.xlsx
+++ b/publication_tables/supplementary/S10_macro_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.0914690647</v>
+        <v>27.09146906470148</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.33146835171e-13</v>
+        <v>-2.775557561562891e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>1.06581410364e-12</v>
+        <v>1.110223024625157e-12</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.000000000000003</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -544,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.43864198482</v>
+        <v>4.438641984824786</v>
       </c>
       <c r="O2" t="n">
-        <v>0.852798860698</v>
+        <v>0.85279886069821</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F3" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G3" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -598,10 +598,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -619,43 +619,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.3192550778</v>
+        <v>27.35432873123547</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.292207907821</v>
+        <v>-0.2994227901914837</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3694943312</v>
+        <v>-2.358030379390585</v>
       </c>
       <c r="F4" t="n">
-        <v>1.010261273</v>
+        <v>1.011850482021188</v>
       </c>
       <c r="G4" t="n">
-        <v>1.01183220116</v>
+        <v>1.013767662456683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235086</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.13067475456</v>
+        <v>0.1308130416233192</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00404148725444</v>
+        <v>0.00404576417391709</v>
       </c>
       <c r="M4" t="n">
-        <v>0.134716241815</v>
+        <v>0.1348588057972363</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4835372251</v>
+        <v>4.488694381376724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015143</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -673,43 +673,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.3165681752</v>
+        <v>27.3515094593545</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.291574323254</v>
+        <v>-0.2987773361852408</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3686315681</v>
+        <v>-2.35712896388609</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01014831691</v>
+        <v>1.011732354363258</v>
       </c>
       <c r="G5" t="n">
-        <v>1.01167874197</v>
+        <v>1.013606917898234</v>
       </c>
       <c r="H5" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235124</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000185</v>
       </c>
       <c r="J5" t="n">
-        <v>0.130590949742</v>
+        <v>0.130720359967911</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00403889535285</v>
+        <v>0.004042897730966321</v>
       </c>
       <c r="M5" t="n">
-        <v>0.134629845095</v>
+        <v>0.1347632576988774</v>
       </c>
       <c r="N5" t="n">
-        <v>4.48322234683</v>
+        <v>4.488359744106436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015105</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -727,43 +727,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.3100859976</v>
+        <v>27.34469662936363</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.289982265443</v>
+        <v>-0.2971554835022316</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.36653982448</v>
+        <v>-2.354940181581489</v>
       </c>
       <c r="F6" t="n">
-        <v>1.00987641488</v>
+        <v>1.011447545258281</v>
       </c>
       <c r="G6" t="n">
-        <v>1.01130742531</v>
+        <v>1.013217391217531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235151</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000283</v>
       </c>
       <c r="J6" t="n">
-        <v>0.130406560957</v>
+        <v>0.1305140034115257</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00403319260691</v>
+        <v>0.004036515569428632</v>
       </c>
       <c r="M6" t="n">
-        <v>0.134439753564</v>
+        <v>0.1345505189809544</v>
       </c>
       <c r="N6" t="n">
-        <v>4.48247962461</v>
+        <v>4.487567842487854</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015078</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -781,46 +781,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.2357043327</v>
+        <v>27.22957061039556</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.30274063755</v>
+        <v>-0.2992956319744944</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.38632781473</v>
+        <v>-2.361367092867095</v>
       </c>
       <c r="F7" t="n">
-        <v>1.01251770695</v>
+        <v>1.012289852821915</v>
       </c>
       <c r="G7" t="n">
-        <v>1.01485133101</v>
+        <v>1.014363762686251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235068</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999979</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="N7" t="n">
-        <v>4.49065923661</v>
+        <v>4.49070367090788</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.723817579401516</v>
       </c>
       <c r="P7" t="n">
-        <v>3.61771539492</v>
+        <v>3.594248886224392</v>
       </c>
     </row>
     <row r="8">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.264680607</v>
+        <v>27.30087132726683</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.130135163031</v>
+        <v>-0.1383465289260699</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0432073863727</v>
+        <v>-0.04254547154119992</v>
       </c>
       <c r="F8" t="n">
-        <v>1.00128036281</v>
+        <v>1.002619677848412</v>
       </c>
       <c r="G8" t="n">
-        <v>1.00981306067</v>
+        <v>1.011870522412323</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -868,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.46017268382</v>
+        <v>4.464561141541568</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8590120199720001</v>
+        <v>0.8604015696688543</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -889,43 +889,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.3022394574</v>
+        <v>27.34054424751318</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.146764479222</v>
+        <v>-0.1551939131026026</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.49443746405</v>
+        <v>-1.492388078055207</v>
       </c>
       <c r="F9" t="n">
-        <v>1.00212117623</v>
+        <v>1.003533874392289</v>
       </c>
       <c r="G9" t="n">
-        <v>1.01208166283</v>
+        <v>1.014256038473747</v>
       </c>
       <c r="H9" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.499999999999989</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1307229297</v>
+        <v>0.1308591054364901</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00404297720721</v>
+        <v>0.004047188827932683</v>
       </c>
       <c r="M9" t="n">
-        <v>0.134765906907</v>
+        <v>0.1349062942644227</v>
       </c>
       <c r="N9" t="n">
-        <v>4.46266566634</v>
+        <v>4.467361051418327</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7235546746480001</v>
+        <v>0.7249442243453499</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -943,43 +943,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.2995383017</v>
+        <v>27.33770660434382</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.146125090997</v>
+        <v>-0.154542043111161</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.49355865909</v>
+        <v>-1.49147008328484</v>
       </c>
       <c r="F10" t="n">
-        <v>1.00200828477</v>
+        <v>1.003415708264847</v>
       </c>
       <c r="G10" t="n">
-        <v>1.01192735923</v>
+        <v>1.014094225375939</v>
       </c>
       <c r="H10" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235142</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000251</v>
       </c>
       <c r="J10" t="n">
-        <v>0.130636699536</v>
+        <v>0.1307635399380936</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00404031029492</v>
+        <v>0.004044233193961658</v>
       </c>
       <c r="M10" t="n">
-        <v>0.134677009831</v>
+        <v>0.1348077731320552</v>
       </c>
       <c r="N10" t="n">
-        <v>4.46234958712</v>
+        <v>4.467024559312216</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7235546746480001</v>
+        <v>0.7249442243453401</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -997,43 +997,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.2930117684</v>
+        <v>27.33084254205602</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.144509750998</v>
+        <v>-0.1528961305543586</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.49142542753</v>
+        <v>-1.4892396091016</v>
       </c>
       <c r="F11" t="n">
-        <v>1.00173611709</v>
+        <v>1.003130504974787</v>
       </c>
       <c r="G11" t="n">
-        <v>1.01155349178</v>
+        <v>1.013701787830499</v>
       </c>
       <c r="H11" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235094</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000074</v>
       </c>
       <c r="J11" t="n">
-        <v>0.130445220746</v>
+        <v>0.1305489793342555</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00403438827049</v>
+        <v>0.004037597298997592</v>
       </c>
       <c r="M11" t="n">
-        <v>0.134479609016</v>
+        <v>0.134586576633253</v>
       </c>
       <c r="N11" t="n">
-        <v>4.46160193693</v>
+        <v>4.466226418741057</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7235546746480001</v>
+        <v>0.7249442243453449</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1051,46 +1051,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.2187019553</v>
+        <v>27.21587618008727</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.156792594864</v>
+        <v>-0.1549462487991704</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.51150536035</v>
+        <v>-1.495813375973054</v>
       </c>
       <c r="F12" t="n">
-        <v>1.00438421456</v>
+        <v>1.003976822228539</v>
       </c>
       <c r="G12" t="n">
-        <v>1.01510729751</v>
+        <v>1.014860854053005</v>
       </c>
       <c r="H12" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235098</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000091</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.137385255403</v>
+        <v>0.1360210784373662</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.137385255403</v>
+        <v>0.1360210784373662</v>
       </c>
       <c r="N12" t="n">
-        <v>4.46974607202</v>
+        <v>4.469365405555788</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7235546746480001</v>
+        <v>0.7249442243453444</v>
       </c>
       <c r="P12" t="n">
-        <v>3.61827338489</v>
+        <v>3.607630108428976</v>
       </c>
     </row>
     <row r="13">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.1095811339</v>
+        <v>27.10727847101788</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.148653200709</v>
+        <v>-0.1481445955075489</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.887429394126</v>
+        <v>-0.8770476868163235</v>
       </c>
       <c r="F13" t="n">
-        <v>1.00807077095</v>
+        <v>1.008233109712591</v>
       </c>
       <c r="G13" t="n">
-        <v>0.999808485323</v>
+        <v>0.9996225093558743</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.45971430353</v>
+        <v>4.460286278049099</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8512257898309999</v>
+        <v>0.8520187662547598</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1159,43 +1159,43 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.1452809393</v>
+        <v>27.14455829704921</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.163617829492</v>
+        <v>-0.1631540039813251</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.33245785453</v>
+        <v>-2.322728697835019</v>
       </c>
       <c r="F14" t="n">
-        <v>1.00896197121</v>
+        <v>1.009185486736381</v>
       </c>
       <c r="G14" t="n">
-        <v>1.00197095684</v>
+        <v>1.001871032642408</v>
       </c>
       <c r="H14" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235117</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.500000000000016</v>
       </c>
       <c r="J14" t="n">
-        <v>0.130596469089</v>
+        <v>0.1307141777650163</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00403906605431</v>
+        <v>0.004042706528814937</v>
       </c>
       <c r="M14" t="n">
-        <v>0.134635535144</v>
+        <v>0.1347568842938312</v>
       </c>
       <c r="N14" t="n">
-        <v>4.46198870635</v>
+        <v>4.462810596120823</v>
       </c>
       <c r="O14" t="n">
-        <v>0.715768444508</v>
+        <v>0.7165614209312481</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1213,43 +1213,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.1427192126</v>
+        <v>27.14188671028605</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.163055523232</v>
+        <v>-0.1625861137618645</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.33163677704</v>
+        <v>-2.321872565615402</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0088492147</v>
+        <v>1.009068294484462</v>
       </c>
       <c r="G15" t="n">
-        <v>1.00182458431</v>
+        <v>1.001718649478964</v>
       </c>
       <c r="H15" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235052</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999918</v>
       </c>
       <c r="J15" t="n">
-        <v>0.13051910632</v>
+        <v>0.1306290833078819</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00403667339133</v>
+        <v>0.004040074741480884</v>
       </c>
       <c r="M15" t="n">
-        <v>0.134555779711</v>
+        <v>0.1346691580493628</v>
       </c>
       <c r="N15" t="n">
-        <v>4.46168946517</v>
+        <v>4.462494401575175</v>
       </c>
       <c r="O15" t="n">
-        <v>0.715768444508</v>
+        <v>0.7165614209312546</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1267,43 +1267,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.1365408292</v>
+        <v>27.13544007955618</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.161636778695</v>
+        <v>-0.161153508294487</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.32964527602</v>
+        <v>-2.319795167950123</v>
       </c>
       <c r="F16" t="n">
-        <v>1.00857775937</v>
+        <v>1.008786028097143</v>
       </c>
       <c r="G16" t="n">
-        <v>1.00147046204</v>
+        <v>1.001349839513111</v>
       </c>
       <c r="H16" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235102</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000102</v>
       </c>
       <c r="J16" t="n">
-        <v>0.130350430432</v>
+        <v>0.1304417160875178</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00403145661129</v>
+        <v>0.004034279878995396</v>
       </c>
       <c r="M16" t="n">
-        <v>0.134381887043</v>
+        <v>0.1344759959665132</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46098476302</v>
+        <v>4.461748480186651</v>
       </c>
       <c r="O16" t="n">
-        <v>0.715768444508</v>
+        <v>0.7165614209312496</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1321,46 +1321,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.0587353527</v>
+        <v>27.01951034810941</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.171930872785</v>
+        <v>-0.1626939850475906</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.34808395606</v>
+        <v>-2.325930531884812</v>
       </c>
       <c r="F17" t="n">
-        <v>1.01122354726</v>
+        <v>1.009630025219533</v>
       </c>
       <c r="G17" t="n">
-        <v>1.00480632186</v>
+        <v>1.002443577757429</v>
       </c>
       <c r="H17" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235101</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000099</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.137108221324</v>
+        <v>0.1358606091491935</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.137108221324</v>
+        <v>0.1358606091491935</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4687249987</v>
+        <v>4.464773405220588</v>
       </c>
       <c r="O17" t="n">
-        <v>0.715768444508</v>
+        <v>0.7165614209312497</v>
       </c>
       <c r="P17" t="n">
-        <v>3.635587364</v>
+        <v>3.668860641943988</v>
       </c>
     </row>
     <row r="18">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.1954276972</v>
+        <v>27.21324736801715</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.104247345325</v>
+        <v>-0.1069954291636144</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.518778825213</v>
+        <v>-0.5136298966668562</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0052495826</v>
+        <v>1.00609797874217</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0052588651</v>
+        <v>1.006245024206402</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1408,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.46131414405</v>
+        <v>4.463890717015562</v>
       </c>
       <c r="O18" t="n">
-        <v>0.854765217884</v>
+        <v>0.8558543552660365</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1429,43 +1429,43 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.2321237339</v>
+        <v>27.25180216028126</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.11985393939</v>
+        <v>-0.1227252910465215</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.96573833671</v>
+        <v>-1.960162188013337</v>
       </c>
       <c r="F19" t="n">
-        <v>1.00611536579</v>
+        <v>1.007032556352203</v>
       </c>
       <c r="G19" t="n">
-        <v>1.00747829352</v>
+        <v>1.008566607709438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235062</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999956</v>
       </c>
       <c r="J19" t="n">
-        <v>0.130659980215</v>
+        <v>0.1307868460961783</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00404103031593</v>
+        <v>0.004044954002974587</v>
       </c>
       <c r="M19" t="n">
-        <v>0.134701010531</v>
+        <v>0.1348318000991529</v>
       </c>
       <c r="N19" t="n">
-        <v>4.46370439329</v>
+        <v>4.466560706839831</v>
       </c>
       <c r="O19" t="n">
-        <v>0.71930787256</v>
+        <v>0.7203970099425303</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1483,43 +1483,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.2294873796</v>
+        <v>27.249042213557</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.119259774371</v>
+        <v>-0.1221219639844118</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.96488716548</v>
+        <v>-1.95927391899976</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0060024906</v>
+        <v>1.006914787764761</v>
       </c>
       <c r="G20" t="n">
-        <v>1.00732767615</v>
+        <v>1.008409206845002</v>
       </c>
       <c r="H20" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235043</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999885</v>
       </c>
       <c r="J20" t="n">
-        <v>0.130578083214</v>
+        <v>0.1306964052537119</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00403849741898</v>
+        <v>0.004042156863516864</v>
       </c>
       <c r="M20" t="n">
-        <v>0.134616580633</v>
+        <v>0.1347385621172288</v>
       </c>
       <c r="N20" t="n">
-        <v>4.46339613722</v>
+        <v>4.46623371112369</v>
       </c>
       <c r="O20" t="n">
-        <v>0.71930787256</v>
+        <v>0.7203970099425322</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -1537,43 +1537,43 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27.2231234528</v>
+        <v>27.24237386732862</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.117758386433</v>
+        <v>-0.1205979019376691</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.96282195147</v>
+        <v>-1.957117021184163</v>
       </c>
       <c r="F21" t="n">
-        <v>1.00573058033</v>
+        <v>1.006630840598767</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0069630277</v>
+        <v>1.008027844241631</v>
       </c>
       <c r="H21" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235107</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000123</v>
       </c>
       <c r="J21" t="n">
-        <v>0.130397804688</v>
+        <v>0.1304951836731137</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00403292179447</v>
+        <v>0.004035933515663311</v>
       </c>
       <c r="M21" t="n">
-        <v>0.134430726482</v>
+        <v>0.134531117188777</v>
       </c>
       <c r="N21" t="n">
-        <v>4.46266859513</v>
+        <v>4.465460100821034</v>
       </c>
       <c r="O21" t="n">
-        <v>0.71930787256</v>
+        <v>0.7203970099425258</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -1591,46 +1591,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.1472160843</v>
+        <v>27.12695289552904</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.128773006753</v>
+        <v>-0.1223171031964454</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.98213540055</v>
+        <v>-1.963477396654367</v>
       </c>
       <c r="F22" t="n">
-        <v>1.00837828579</v>
+        <v>1.007476211302374</v>
       </c>
       <c r="G22" t="n">
-        <v>1.01041663657</v>
+        <v>1.009155797301081</v>
       </c>
       <c r="H22" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235084</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000037</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.137252067941</v>
+        <v>0.1359412628619496</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.137252067941</v>
+        <v>0.1359412628619496</v>
       </c>
       <c r="N22" t="n">
-        <v>4.47063073403</v>
+        <v>4.468545579546551</v>
       </c>
       <c r="O22" t="n">
-        <v>0.71930787256</v>
+        <v>0.7203970099425281</v>
       </c>
       <c r="P22" t="n">
-        <v>3.62594917275</v>
+        <v>3.633543160897847</v>
       </c>
     </row>
     <row r="23">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.4157963699</v>
+        <v>27.47281583697596</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.69639168311</v>
+        <v>-0.7160975148733151</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.55595935526</v>
+        <v>-1.536003121483254</v>
       </c>
       <c r="F23" t="n">
-        <v>1.01551978506</v>
+        <v>1.017977733639786</v>
       </c>
       <c r="G23" t="n">
-        <v>1.01613007634</v>
+        <v>1.019262300114992</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1678,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5136461008</v>
+        <v>4.522250668738676</v>
       </c>
       <c r="O23" t="n">
-        <v>0.862411003776</v>
+        <v>0.8662926701055511</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -1699,43 +1699,43 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.4543827958</v>
+        <v>27.51383404981266</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.713606813399</v>
+        <v>-0.7336158098985801</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.97638808416</v>
+        <v>-2.954079275797183</v>
       </c>
       <c r="F24" t="n">
-        <v>1.01634952649</v>
+        <v>1.018897746988239</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01845869622</v>
+        <v>1.02172512292157</v>
       </c>
       <c r="H24" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235077</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000012</v>
       </c>
       <c r="J24" t="n">
-        <v>0.130695992436</v>
+        <v>0.1308539035090565</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00404214409595</v>
+        <v>0.004047027943579068</v>
       </c>
       <c r="M24" t="n">
-        <v>0.134738136532</v>
+        <v>0.1349009314526356</v>
       </c>
       <c r="N24" t="n">
-        <v>4.51623896287</v>
+        <v>4.52520093797444</v>
       </c>
       <c r="O24" t="n">
-        <v>0.726953658452</v>
+        <v>0.7308353247820434</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -1753,43 +1753,43 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.4516187406</v>
+        <v>27.51092351487777</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.712884284127</v>
+        <v>-0.7328775047020675</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.97550866376</v>
+        <v>-2.953158388107102</v>
       </c>
       <c r="F25" t="n">
-        <v>1.01623653558</v>
+        <v>1.018779176809852</v>
       </c>
       <c r="G25" t="n">
-        <v>1.01830090593</v>
+        <v>1.021559237836301</v>
       </c>
       <c r="H25" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235188</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000422</v>
       </c>
       <c r="J25" t="n">
-        <v>0.13060928306</v>
+        <v>0.1307578275324434</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00403946236269</v>
+        <v>0.004044056521621962</v>
       </c>
       <c r="M25" t="n">
-        <v>0.134648745423</v>
+        <v>0.1348018840540654</v>
       </c>
       <c r="N25" t="n">
-        <v>4.51591387792</v>
+        <v>4.52485449496423</v>
       </c>
       <c r="O25" t="n">
-        <v>0.726953658452</v>
+        <v>0.7308353247820323</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -1807,43 +1807,43 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.4449561077</v>
+        <v>27.50388843150902</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.711086357698</v>
+        <v>-0.7310396449972667</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.97337899248</v>
+        <v>-2.950922489706187</v>
       </c>
       <c r="F26" t="n">
-        <v>1.01596484853</v>
+        <v>1.018493298995368</v>
       </c>
       <c r="G26" t="n">
-        <v>1.01791942648</v>
+        <v>1.021157156890924</v>
       </c>
       <c r="H26" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235148</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000274</v>
       </c>
       <c r="J26" t="n">
-        <v>0.130418677031</v>
+        <v>0.1305437633586401</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00403356733086</v>
+        <v>0.004037435980164127</v>
       </c>
       <c r="M26" t="n">
-        <v>0.134452244362</v>
+        <v>0.1345811993388042</v>
       </c>
       <c r="N26" t="n">
-        <v>4.51514778716</v>
+        <v>4.524034391703156</v>
       </c>
       <c r="O26" t="n">
-        <v>0.726953658452</v>
+        <v>0.7308353247820363</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -1861,46 +1861,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.3729176567</v>
+        <v>27.38921074917758</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.727706704484</v>
+        <v>-0.7341292146895162</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.99383445479</v>
+        <v>-2.957443940380367</v>
       </c>
       <c r="F27" t="n">
-        <v>1.01859276835</v>
+        <v>1.019329870149276</v>
       </c>
       <c r="G27" t="n">
-        <v>1.02160179031</v>
+        <v>1.022331554515186</v>
       </c>
       <c r="H27" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235091</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000062</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.137471915056</v>
+        <v>0.1360446668830413</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.137471915056</v>
+        <v>0.1360446668830413</v>
       </c>
       <c r="N27" t="n">
-        <v>4.52366281667</v>
+        <v>4.527248668554442</v>
       </c>
       <c r="O27" t="n">
-        <v>0.726953658452</v>
+        <v>0.7308353247820421</v>
       </c>
       <c r="P27" t="n">
-        <v>3.60525269277</v>
+        <v>3.536667163933072</v>
       </c>
     </row>
     <row r="28">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F28" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G28" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -1969,43 +1969,43 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3005547513</v>
+        <v>27.33458779462902</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.284208341188</v>
+        <v>-0.2913362119988827</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.65180836993</v>
+        <v>-1.64097070131306</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0098362983</v>
+        <v>1.011386618111305</v>
       </c>
       <c r="G29" t="n">
-        <v>1.010702082</v>
+        <v>1.012580233198728</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06772867266179999</v>
+        <v>0.06772867266175908</v>
       </c>
       <c r="I29" t="n">
-        <v>0.25</v>
+        <v>0.2500000000000199</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0653381188874</v>
+        <v>0.06540712818421221</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00202076656353</v>
+        <v>0.002022900871676666</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06735888545090001</v>
+        <v>0.06743002905588888</v>
       </c>
       <c r="N29" t="n">
-        <v>4.48230519247</v>
+        <v>4.487307582916628</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7894442192110001</v>
+        <v>0.7915462520632638</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -2023,43 +2023,43 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.299210778</v>
+        <v>27.33317769343648</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.283891509032</v>
+        <v>-0.2910135007241355</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.65133774255</v>
+        <v>-1.640478970276749</v>
       </c>
       <c r="F30" t="n">
-        <v>1.00977980325</v>
+        <v>1.011327539555103</v>
       </c>
       <c r="G30" t="n">
-        <v>1.01062532314</v>
+        <v>1.012499834896227</v>
       </c>
       <c r="H30" t="n">
-        <v>0.06772867266179999</v>
+        <v>0.0677286726617552</v>
       </c>
       <c r="I30" t="n">
-        <v>0.25</v>
+        <v>0.2500000000000056</v>
       </c>
       <c r="J30" t="n">
-        <v>0.06529624165380001</v>
+        <v>0.06536081943408573</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00201947139136</v>
+        <v>0.002021468642291311</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0673157130452</v>
+        <v>0.06738228807637704</v>
       </c>
       <c r="N30" t="n">
-        <v>4.48214768362</v>
+        <v>4.487140201272175</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7894442192110001</v>
+        <v>0.7915462520632677</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2077,43 +2077,43 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.2959680528</v>
+        <v>27.32976986313532</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.283095283237</v>
+        <v>-0.2902025021858545</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.65019721402</v>
+        <v>-1.639285538978053</v>
       </c>
       <c r="F31" t="n">
-        <v>1.00964379712</v>
+        <v>1.011185088386689</v>
       </c>
       <c r="G31" t="n">
-        <v>1.01043957374</v>
+        <v>1.012304992888129</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06772867266179999</v>
+        <v>0.06772867266175009</v>
       </c>
       <c r="I31" t="n">
-        <v>0.25</v>
+        <v>0.2499999999999867</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0652040641822</v>
+        <v>0.06525767965626933</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00201662054172</v>
+        <v>0.002018278752255753</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0672206847239</v>
+        <v>0.06727595840852509</v>
       </c>
       <c r="N31" t="n">
-        <v>4.48177609387</v>
+        <v>4.486744051127453</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7894442192110001</v>
+        <v>0.7915462520632728</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2131,46 +2131,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.258797937</v>
+        <v>27.27216036043371</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.289472460522</v>
+        <v>-0.2912582742194414</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.66102011047</v>
+        <v>-1.642774321716967</v>
       </c>
       <c r="F32" t="n">
-        <v>1.01096503124</v>
+        <v>1.011604142780686</v>
       </c>
       <c r="G32" t="n">
-        <v>1.01221268337</v>
+        <v>1.012875451554772</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06772867266179999</v>
+        <v>0.06772867266175597</v>
       </c>
       <c r="I32" t="n">
-        <v>0.25</v>
+        <v>0.2500000000000084</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06866993636219999</v>
+        <v>0.06798942918901271</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06866993636219999</v>
+        <v>0.06798942918901271</v>
       </c>
       <c r="N32" t="n">
-        <v>4.48586889292</v>
+        <v>4.4883063768153</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7894442192110001</v>
+        <v>0.7915462520632669</v>
       </c>
       <c r="P32" t="n">
-        <v>1.84540853445</v>
+        <v>1.813487777585447</v>
       </c>
     </row>
     <row r="33">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F33" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G33" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2218,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -2239,43 +2239,43 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.3565496643</v>
+        <v>27.39371433215107</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.308234005894</v>
+        <v>-0.3156255773741234</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.80171458246</v>
+        <v>-3.78883719332046</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01110373696</v>
+        <v>1.012770963387523</v>
       </c>
       <c r="G34" t="n">
-        <v>1.01408666278</v>
+        <v>1.016137289903504</v>
       </c>
       <c r="H34" t="n">
-        <v>0.270914690647</v>
+        <v>0.2709146906470205</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.000000000000021</v>
       </c>
       <c r="J34" t="n">
-        <v>0.261343595418</v>
+        <v>0.2616212371123084</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.00808279161086</v>
+        <v>0.008091378467390983</v>
       </c>
       <c r="M34" t="n">
-        <v>0.269426387029</v>
+        <v>0.2697126155796994</v>
       </c>
       <c r="N34" t="n">
-        <v>4.48598451456</v>
+        <v>4.491452562828836</v>
       </c>
       <c r="O34" t="n">
-        <v>0.586258201226</v>
+        <v>0.5883602340780024</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -2293,43 +2293,43 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>27.3511800142</v>
+        <v>27.38807949248251</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.306967198558</v>
+        <v>-0.3143345918246276</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.8003012319</v>
+        <v>-3.787360654957639</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0108779586</v>
+        <v>1.012534823710949</v>
       </c>
       <c r="G35" t="n">
-        <v>1.01377997735</v>
+        <v>1.015816007998105</v>
       </c>
       <c r="H35" t="n">
-        <v>0.270914690647</v>
+        <v>0.2709146906470161</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.000000000000005</v>
       </c>
       <c r="J35" t="n">
-        <v>0.261175786237</v>
+        <v>0.2614356192351865</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00807760163618</v>
+        <v>0.008085637708304737</v>
       </c>
       <c r="M35" t="n">
-        <v>0.269253387873</v>
+        <v>0.2695212569434912</v>
       </c>
       <c r="N35" t="n">
-        <v>4.48535531256</v>
+        <v>4.490783789505787</v>
       </c>
       <c r="O35" t="n">
-        <v>0.586258201226</v>
+        <v>0.5883602340780067</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -2347,43 +2347,43 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27.338228692</v>
+        <v>27.37446510779575</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.303784752742</v>
+        <v>-0.3110915695998862</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.79687087953</v>
+        <v>-3.783771138678182</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01033458991</v>
+        <v>1.011965573016277</v>
       </c>
       <c r="G36" t="n">
-        <v>1.01303806947</v>
+        <v>1.015037581434986</v>
       </c>
       <c r="H36" t="n">
-        <v>0.270914690647</v>
+        <v>0.2709146906470176</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.00000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>0.260806876212</v>
+        <v>0.2610226016742424</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0080661920478</v>
+        <v>0.008072863969306466</v>
       </c>
       <c r="M36" t="n">
-        <v>0.26887306826</v>
+        <v>0.2690954656435489</v>
       </c>
       <c r="N36" t="n">
-        <v>4.483871688</v>
+        <v>4.489201573119218</v>
       </c>
       <c r="O36" t="n">
-        <v>0.586258201226</v>
+        <v>0.5883602340780053</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -2401,46 +2401,46 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27.189301236</v>
+        <v>27.14458564457134</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.329315889847</v>
+        <v>-0.3154862445691964</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.82908600306</v>
+        <v>-3.794400676789089</v>
       </c>
       <c r="F37" t="n">
-        <v>1.01561256193</v>
+        <v>1.013667034409568</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02011671326</v>
+        <v>1.017352181314104</v>
       </c>
       <c r="H37" t="n">
-        <v>0.270914690647</v>
+        <v>0.270914690647011</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.9999999999999861</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.274677828687</v>
+        <v>0.2719727551456184</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.274677828687</v>
+        <v>0.2719727551456184</v>
       </c>
       <c r="N37" t="n">
-        <v>4.50020720073</v>
+        <v>4.495518008734873</v>
       </c>
       <c r="O37" t="n">
-        <v>0.586258201226</v>
+        <v>0.5883602340780119</v>
       </c>
       <c r="P37" t="n">
-        <v>6.95978751009</v>
+        <v>7.059993508597737</v>
       </c>
     </row>
     <row r="38">
@@ -2455,19 +2455,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>27.2243875916</v>
+        <v>27.25615770902845</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.252269164082</v>
+        <v>-0.2594935738161275</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.04506642434</v>
+        <v>-1.035679290768654</v>
       </c>
       <c r="F38" t="n">
-        <v>1.01166505301</v>
+        <v>1.013331689086966</v>
       </c>
       <c r="G38" t="n">
-        <v>1.0066230195</v>
+        <v>1.008379741650684</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2488,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.46918825321</v>
+        <v>4.473804651198181</v>
       </c>
       <c r="O38" t="n">
-        <v>0.84773974463</v>
+        <v>0.8496617818193513</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -2509,43 +2509,43 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27.2615896878</v>
+        <v>27.2954086363965</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.267794082208</v>
+        <v>-0.2751710129921148</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.48328817705</v>
+        <v>-2.47272008573709</v>
       </c>
       <c r="F39" t="n">
-        <v>1.01232172026</v>
+        <v>1.014063866477895</v>
       </c>
       <c r="G39" t="n">
-        <v>1.00887395606</v>
+        <v>1.010743592149936</v>
       </c>
       <c r="H39" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235116</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000157</v>
       </c>
       <c r="J39" t="n">
-        <v>0.130663608541</v>
+        <v>0.1307983848099966</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.00404114253219</v>
+        <v>0.004045310870412266</v>
       </c>
       <c r="M39" t="n">
-        <v>0.134704751073</v>
+        <v>0.1348436956804089</v>
       </c>
       <c r="N39" t="n">
-        <v>4.47159753946</v>
+        <v>4.476517453595894</v>
       </c>
       <c r="O39" t="n">
-        <v>0.712282399306</v>
+        <v>0.7142044364958396</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -2563,43 +2563,43 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27.2589203021</v>
+        <v>27.29260645824156</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.267167439631</v>
+        <v>-0.2745325463945902</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.48244505331</v>
+        <v>-2.471838765263956</v>
       </c>
       <c r="F40" t="n">
-        <v>1.01220611572</v>
+        <v>1.013942988466436</v>
       </c>
       <c r="G40" t="n">
-        <v>1.0087215294</v>
+        <v>1.010583859343602</v>
       </c>
       <c r="H40" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235136</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.500000000000023</v>
       </c>
       <c r="J40" t="n">
-        <v>0.13058083298</v>
+        <v>0.1307067029455232</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0040385824633</v>
+        <v>0.004042475348830616</v>
       </c>
       <c r="M40" t="n">
-        <v>0.134619415443</v>
+        <v>0.1347491782943538</v>
       </c>
       <c r="N40" t="n">
-        <v>4.47128421833</v>
+        <v>4.476184271361613</v>
       </c>
       <c r="O40" t="n">
-        <v>0.712282399306</v>
+        <v>0.7142044364958376</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -2617,43 +2617,43 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27.2524803146</v>
+        <v>27.28583477960168</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.265592511692</v>
+        <v>-0.272927976141446</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.48039897881</v>
+        <v>-2.469696695674362</v>
       </c>
       <c r="F41" t="n">
-        <v>1.01192834354</v>
+        <v>1.013652072506764</v>
       </c>
       <c r="G41" t="n">
-        <v>1.00835270216</v>
+        <v>1.010196770911068</v>
       </c>
       <c r="H41" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235124</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.130398786593</v>
+        <v>0.1305026177318983</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.00403295216266</v>
+        <v>0.004036163435007163</v>
       </c>
       <c r="M41" t="n">
-        <v>0.134431738755</v>
+        <v>0.1345387811669054</v>
       </c>
       <c r="N41" t="n">
-        <v>4.47054520718</v>
+        <v>4.475395833001506</v>
       </c>
       <c r="O41" t="n">
-        <v>0.712282399306</v>
+        <v>0.7142044364958389</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -2671,46 +2671,46 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>27.1775021989</v>
+        <v>27.17059123320977</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.278105834905</v>
+        <v>-0.2750040457394243</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.49955210923</v>
+        <v>-2.475966019800113</v>
       </c>
       <c r="F42" t="n">
-        <v>1.01466131953</v>
+        <v>1.014517358609394</v>
       </c>
       <c r="G42" t="n">
-        <v>1.01185904374</v>
+        <v>1.011335012102945</v>
       </c>
       <c r="H42" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235071</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999988</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.137280161949</v>
+        <v>0.1359567248314925</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.137280161949</v>
+        <v>0.1359567248314925</v>
       </c>
       <c r="N42" t="n">
-        <v>4.47864960141</v>
+        <v>4.478515175059159</v>
       </c>
       <c r="O42" t="n">
-        <v>0.712282399306</v>
+        <v>0.7142044364958442</v>
       </c>
       <c r="P42" t="n">
-        <v>3.62325660172</v>
+        <v>3.598055101887761</v>
       </c>
     </row>
     <row r="43">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.3347500518</v>
+        <v>27.36891041698469</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.298210978104</v>
+        <v>-0.3051768915896202</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.818923931871</v>
+        <v>-0.8075681463850182</v>
       </c>
       <c r="F43" t="n">
-        <v>1.00868197138</v>
+        <v>1.01012980909477</v>
       </c>
       <c r="G43" t="n">
-        <v>1.01224717085</v>
+        <v>1.014128312513925</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.49261799713</v>
+        <v>4.497701485795081</v>
       </c>
       <c r="O43" t="n">
-        <v>0.866313581963</v>
+        <v>0.8685868353382999</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -2779,43 +2779,43 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>27.3723970357</v>
+        <v>27.40865751564447</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.314553224794</v>
+        <v>-0.3217053164182415</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.2536794524</v>
+        <v>-2.241097411133586</v>
       </c>
       <c r="F44" t="n">
-        <v>1.00965622095</v>
+        <v>1.011182828151427</v>
       </c>
       <c r="G44" t="n">
-        <v>1.01452015352</v>
+        <v>1.01651689619338</v>
       </c>
       <c r="H44" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235026</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999825</v>
       </c>
       <c r="J44" t="n">
-        <v>0.130684277675</v>
+        <v>0.1308253446633196</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00404178178377</v>
+        <v>0.004046144680308853</v>
       </c>
       <c r="M44" t="n">
-        <v>0.134726059459</v>
+        <v>0.1348714893436284</v>
       </c>
       <c r="N44" t="n">
-        <v>4.49513140349</v>
+        <v>4.500528157799432</v>
       </c>
       <c r="O44" t="n">
-        <v>0.73085623664</v>
+        <v>0.7331294900147973</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -2833,43 +2833,43 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>27.369694952</v>
+        <v>27.40582333217292</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.313911990924</v>
+        <v>-0.3210520525404381</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.25280206275</v>
+        <v>-2.240181052495682</v>
       </c>
       <c r="F45" t="n">
-        <v>1.00954464828</v>
+        <v>1.011066139100266</v>
       </c>
       <c r="G45" t="n">
-        <v>1.01436580793</v>
+        <v>1.016355278339445</v>
       </c>
       <c r="H45" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235044</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999891</v>
       </c>
       <c r="J45" t="n">
-        <v>0.130599594096</v>
+        <v>0.1307317993855015</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.00403916270399</v>
+        <v>0.004043251527386643</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1346387568</v>
+        <v>0.1347750509128881</v>
       </c>
       <c r="N45" t="n">
-        <v>4.49481504532</v>
+        <v>4.500192107499331</v>
       </c>
       <c r="O45" t="n">
-        <v>0.73085623664</v>
+        <v>0.7331294900147955</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -2887,43 +2887,43 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>27.3631760357</v>
+        <v>27.39897449679757</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.312301281394</v>
+        <v>-0.3194111374064446</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.25067590466</v>
+        <v>-2.237957129740986</v>
       </c>
       <c r="F46" t="n">
-        <v>1.00927576323</v>
+        <v>1.010784478894102</v>
       </c>
       <c r="G46" t="n">
-        <v>1.01399234163</v>
+        <v>1.015963638276959</v>
       </c>
       <c r="H46" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235142</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000251</v>
       </c>
       <c r="J46" t="n">
-        <v>0.130413217002</v>
+        <v>0.1305234947514437</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.00403339846397</v>
+        <v>0.004036809116024033</v>
       </c>
       <c r="M46" t="n">
-        <v>0.134446615466</v>
+        <v>0.1345603038674678</v>
       </c>
       <c r="N46" t="n">
-        <v>4.49406881152</v>
+        <v>4.499396867116999</v>
       </c>
       <c r="O46" t="n">
-        <v>0.73085623664</v>
+        <v>0.7331294900147858</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -2941,46 +2941,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>27.2893274155</v>
+        <v>27.28395337457358</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.325332275162</v>
+        <v>-0.3216227554438622</v>
       </c>
       <c r="E47" t="n">
-        <v>-2.27092016021</v>
+        <v>-2.244499166551939</v>
       </c>
       <c r="F47" t="n">
-        <v>1.01187039936</v>
+        <v>1.011614748326024</v>
       </c>
       <c r="G47" t="n">
-        <v>1.01756940754</v>
+        <v>1.017117132723872</v>
       </c>
       <c r="H47" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235052</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999919</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.137394243583</v>
+        <v>0.1360031825552973</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.137394243583</v>
+        <v>0.1360031825552973</v>
       </c>
       <c r="N47" t="n">
-        <v>4.50232359425</v>
+        <v>4.502549320936716</v>
       </c>
       <c r="O47" t="n">
-        <v>0.73085623664</v>
+        <v>0.7331294900147948</v>
       </c>
       <c r="P47" t="n">
-        <v>3.61271930785</v>
+        <v>3.590613132506918</v>
       </c>
     </row>
     <row r="48">
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>27.3317059898</v>
+        <v>27.37733261064038</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.275531525331</v>
+        <v>-0.2825727426469693</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.904953535021</v>
+        <v>-0.8879500157542353</v>
       </c>
       <c r="F48" t="n">
-        <v>1.01135023782</v>
+        <v>1.013355094559212</v>
       </c>
       <c r="G48" t="n">
-        <v>1.01225408116</v>
+        <v>1.014756595536432</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.48946712228</v>
+        <v>4.496412285434802</v>
       </c>
       <c r="O48" t="n">
-        <v>0.861569500137</v>
+        <v>0.8647545534903465</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3049,43 +3049,43 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27.3812188677</v>
+        <v>27.43023668009644</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.29147649481</v>
+        <v>-0.298727617127148</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.34247036059</v>
+        <v>-2.32400686289681</v>
       </c>
       <c r="F49" t="n">
-        <v>1.01266827901</v>
+        <v>1.014801864839896</v>
       </c>
       <c r="G49" t="n">
-        <v>1.01516789724</v>
+        <v>1.017856134302941</v>
       </c>
       <c r="H49" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235037</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999862</v>
       </c>
       <c r="J49" t="n">
-        <v>0.131679252559</v>
+        <v>0.1319208059419727</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.00407255420284</v>
+        <v>0.004080024926040393</v>
       </c>
       <c r="M49" t="n">
-        <v>0.135751806761</v>
+        <v>0.1360008308680131</v>
       </c>
       <c r="N49" t="n">
-        <v>4.49394103672</v>
+        <v>4.50140666904697</v>
       </c>
       <c r="O49" t="n">
-        <v>0.726112154813</v>
+        <v>0.7292972081668427</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -3103,43 +3103,43 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>27.3776862387</v>
+        <v>27.42648263363084</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.290840456173</v>
+        <v>-0.2980764302897732</v>
       </c>
       <c r="E50" t="n">
-        <v>-2.34134758876</v>
+        <v>-2.322818605022059</v>
       </c>
       <c r="F50" t="n">
-        <v>1.01252266371</v>
+        <v>1.014647612938179</v>
       </c>
       <c r="G50" t="n">
-        <v>1.01496874319</v>
+        <v>1.017644854633944</v>
       </c>
       <c r="H50" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235073</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999993</v>
       </c>
       <c r="J50" t="n">
-        <v>0.131526069586</v>
+        <v>0.1317518431317511</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.00406781658512</v>
+        <v>0.004074799272116012</v>
       </c>
       <c r="M50" t="n">
-        <v>0.135593886171</v>
+        <v>0.1358266424038671</v>
       </c>
       <c r="N50" t="n">
-        <v>4.49348673936</v>
+        <v>4.500918380272863</v>
       </c>
       <c r="O50" t="n">
-        <v>0.726112154813</v>
+        <v>0.7292972081668392</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -3157,43 +3157,43 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>27.3691730417</v>
+        <v>27.41742193935786</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.289245081885</v>
+        <v>-0.2964436481249444</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.33863079422</v>
+        <v>-2.31993928333124</v>
       </c>
       <c r="F51" t="n">
-        <v>1.01217237208</v>
+        <v>1.01427598214623</v>
       </c>
       <c r="G51" t="n">
-        <v>1.01448771941</v>
+        <v>1.017133837767998</v>
       </c>
       <c r="H51" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235096</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000079</v>
       </c>
       <c r="J51" t="n">
-        <v>0.13117459637</v>
+        <v>0.1313615385370356</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.00405694627948</v>
+        <v>0.004062727995990791</v>
       </c>
       <c r="M51" t="n">
-        <v>0.135231542649</v>
+        <v>0.1354242665330264</v>
       </c>
       <c r="N51" t="n">
-        <v>4.49240874466</v>
+        <v>4.499756492678142</v>
       </c>
       <c r="O51" t="n">
-        <v>0.726112154813</v>
+        <v>0.7292972081668369</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -3211,46 +3211,46 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>27.3125614385</v>
+        <v>27.30755810038957</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.302162474149</v>
+        <v>-0.2986079884773618</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.36461014983</v>
+        <v>-2.328420870307801</v>
       </c>
       <c r="F52" t="n">
-        <v>1.01559840152</v>
+        <v>1.015377227786899</v>
       </c>
       <c r="G52" t="n">
-        <v>1.01912721504</v>
+        <v>1.018642396277068</v>
       </c>
       <c r="H52" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235079</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000019</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.139831639513</v>
+        <v>0.1374259636107024</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.139831639513</v>
+        <v>0.1374259636107024</v>
       </c>
       <c r="N52" t="n">
-        <v>4.50391592488</v>
+        <v>4.504000772411629</v>
       </c>
       <c r="O52" t="n">
-        <v>0.726112154813</v>
+        <v>0.7292972081668385</v>
       </c>
       <c r="P52" t="n">
-        <v>3.67074562905</v>
+        <v>3.620648981590825</v>
       </c>
     </row>
     <row r="53">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>27.2498638792</v>
+        <v>27.27552258653748</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.276654380244</v>
+        <v>-0.2836888526608239</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.951128581778</v>
+        <v>-0.9447862822935527</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0081652696</v>
+        <v>1.009390118143141</v>
       </c>
       <c r="G53" t="n">
-        <v>1.00785076725</v>
+        <v>1.00927583667685</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.47568719835</v>
+        <v>4.479318554602997</v>
       </c>
       <c r="O53" t="n">
-        <v>0.854356333915</v>
+        <v>0.8558307187534666</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -3319,43 +3319,43 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>27.2796402454</v>
+        <v>27.30671372196529</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.292671361386</v>
+        <v>-0.2998559971153836</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.38689795842</v>
+        <v>-2.379542893267705</v>
       </c>
       <c r="F54" t="n">
-        <v>1.00872242321</v>
+        <v>1.009999149917723</v>
       </c>
       <c r="G54" t="n">
-        <v>1.00969962696</v>
+        <v>1.011203086070865</v>
       </c>
       <c r="H54" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235062</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999958</v>
       </c>
       <c r="J54" t="n">
-        <v>0.130037481063</v>
+        <v>0.1301243466555351</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.00402177776482</v>
+        <v>0.004024464329552633</v>
       </c>
       <c r="M54" t="n">
-        <v>0.134059258827</v>
+        <v>0.1341488109850878</v>
       </c>
       <c r="N54" t="n">
-        <v>4.47688567141</v>
+        <v>4.480720124561341</v>
       </c>
       <c r="O54" t="n">
-        <v>0.718898988592</v>
+        <v>0.7203733734299604</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -3373,43 +3373,43 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>27.2774833582</v>
+        <v>27.30446835790769</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.292039486711</v>
+        <v>-0.2992142064897174</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.3861978634</v>
+        <v>-2.37881725059742</v>
       </c>
       <c r="F55" t="n">
-        <v>1.00862993435</v>
+        <v>1.009903200842408</v>
       </c>
       <c r="G55" t="n">
-        <v>1.00957480516</v>
+        <v>1.011073368273602</v>
       </c>
       <c r="H55" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235054</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999929</v>
       </c>
       <c r="J55" t="n">
-        <v>0.129997158907</v>
+        <v>0.1300784985232742</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.00402053068784</v>
+        <v>0.004023046346080646</v>
       </c>
       <c r="M55" t="n">
-        <v>0.134017689595</v>
+        <v>0.1341015448693549</v>
       </c>
       <c r="N55" t="n">
-        <v>4.47665815929</v>
+        <v>4.480479813314303</v>
       </c>
       <c r="O55" t="n">
-        <v>0.718898988592</v>
+        <v>0.7203733734299612</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -3427,43 +3427,43 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27.2722776495</v>
+        <v>27.29903976448614</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.290449905467</v>
+        <v>-0.2975994082948241</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.38449821209</v>
+        <v>-2.377052806835001</v>
       </c>
       <c r="F56" t="n">
-        <v>1.00840729829</v>
+        <v>1.009671856239278</v>
       </c>
       <c r="G56" t="n">
-        <v>1.00927243894</v>
+        <v>1.010758656478954</v>
       </c>
       <c r="H56" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235024</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999818</v>
       </c>
       <c r="J56" t="n">
-        <v>0.129917792015</v>
+        <v>0.1299854222249604</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.00401807604169</v>
+        <v>0.004020167697679187</v>
       </c>
       <c r="M56" t="n">
-        <v>0.133935868056</v>
+        <v>0.1340055899226396</v>
       </c>
       <c r="N56" t="n">
-        <v>4.47612613639</v>
+        <v>4.479915731792354</v>
       </c>
       <c r="O56" t="n">
-        <v>0.718898988592</v>
+        <v>0.7203733734299642</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -3481,46 +3481,46 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>27.1869285747</v>
+        <v>27.1806986084503</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.303105273225</v>
+        <v>-0.299723831952603</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.4004626594</v>
+        <v>-2.382222905523723</v>
       </c>
       <c r="F57" t="n">
-        <v>1.01056361606</v>
+        <v>1.010355487502121</v>
       </c>
       <c r="G57" t="n">
-        <v>1.01213924907</v>
+        <v>1.011683077257556</v>
       </c>
       <c r="H57" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235028</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999835</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.135784861752</v>
+        <v>0.1350865514154673</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.135784861752</v>
+        <v>0.1350865514154673</v>
       </c>
       <c r="N57" t="n">
-        <v>4.48224953287</v>
+        <v>4.482372320860229</v>
       </c>
       <c r="O57" t="n">
-        <v>0.718898988592</v>
+        <v>0.7203733734299638</v>
       </c>
       <c r="P57" t="n">
-        <v>3.58455125092</v>
+        <v>3.577889173998836</v>
       </c>
     </row>
     <row r="58">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F58" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G58" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -3568,10 +3568,10 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -3589,28 +3589,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>27.3282439774</v>
+        <v>27.36372548634988</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.291502541103</v>
+        <v>-0.2987495503254278</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.37218626129</v>
+        <v>-2.36084058792535</v>
       </c>
       <c r="F59" t="n">
-        <v>1.010594743</v>
+        <v>1.012199872407944</v>
       </c>
       <c r="G59" t="n">
-        <v>1.01230636232</v>
+        <v>1.014264126565877</v>
       </c>
       <c r="H59" t="n">
-        <v>0.135457345324</v>
+        <v>0.135457345323505</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.499999999999991</v>
       </c>
       <c r="J59" t="n">
-        <v>0.135673188969</v>
+        <v>0.1358463901438051</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.135673188969</v>
+        <v>0.1358463901438051</v>
       </c>
       <c r="N59" t="n">
-        <v>4.48519699795</v>
+        <v>4.490417272314555</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015179</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -3643,28 +3643,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27.3254476115</v>
+        <v>27.36079012294933</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.290844627068</v>
+        <v>-0.2980791288186513</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.37128968896</v>
+        <v>-2.359903517353268</v>
       </c>
       <c r="F60" t="n">
-        <v>1.01047722082</v>
+        <v>1.012076919308422</v>
       </c>
       <c r="G60" t="n">
-        <v>1.01214667999</v>
+        <v>1.014096794281771</v>
       </c>
       <c r="H60" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235044</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.499999999999989</v>
       </c>
       <c r="J60" t="n">
-        <v>0.135582734493</v>
+        <v>0.1357463195070847</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3673,13 +3673,13 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.135582734493</v>
+        <v>0.1357463195070847</v>
       </c>
       <c r="N60" t="n">
-        <v>4.4848688479</v>
+        <v>4.490068370244845</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015185</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -3697,28 +3697,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>27.3187031882</v>
+        <v>27.35369867578131</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.28919150418</v>
+        <v>-0.2963946405353468</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.36911648991</v>
+        <v>-2.357628692700764</v>
       </c>
       <c r="F61" t="n">
-        <v>1.01019439656</v>
+        <v>1.011780548314434</v>
       </c>
       <c r="G61" t="n">
-        <v>1.01176040731</v>
+        <v>1.013691410613185</v>
       </c>
       <c r="H61" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235104</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000111</v>
       </c>
       <c r="J61" t="n">
-        <v>0.135383711241</v>
+        <v>0.1355235102363781</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.135383711241</v>
+        <v>0.1355235102363781</v>
       </c>
       <c r="N61" t="n">
-        <v>4.48409505567</v>
+        <v>4.489242953499827</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015125</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -3751,46 +3751,46 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>27.2357043327</v>
+        <v>27.22957061039556</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.30274063755</v>
+        <v>-0.2992956319744944</v>
       </c>
       <c r="E62" t="n">
-        <v>-2.38632781473</v>
+        <v>-2.361367092867095</v>
       </c>
       <c r="F62" t="n">
-        <v>1.01251770695</v>
+        <v>1.012289852821915</v>
       </c>
       <c r="G62" t="n">
-        <v>1.01485133101</v>
+        <v>1.014363762686251</v>
       </c>
       <c r="H62" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235068</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999979</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="N62" t="n">
-        <v>4.49065923661</v>
+        <v>4.49070367090788</v>
       </c>
       <c r="O62" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.723817579401516</v>
       </c>
       <c r="P62" t="n">
-        <v>3.61771539492</v>
+        <v>3.594248886224392</v>
       </c>
     </row>
     <row r="63">
@@ -3805,19 +3805,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F63" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G63" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -3859,43 +3859,43 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.298770566</v>
+        <v>27.33293122810182</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.293825739026</v>
+        <v>-0.3009671606286402</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.36334645225</v>
+        <v>-2.351616684317459</v>
       </c>
       <c r="F64" t="n">
-        <v>1.00950127891</v>
+        <v>1.011054816221917</v>
       </c>
       <c r="G64" t="n">
-        <v>1.01075165675</v>
+        <v>1.012637164328534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235067</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999976</v>
       </c>
       <c r="J64" t="n">
-        <v>0.119282344535</v>
+        <v>0.1193493839068965</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0132535938372</v>
+        <v>0.01326104265632183</v>
       </c>
       <c r="M64" t="n">
-        <v>0.132535938372</v>
+        <v>0.1326104265632183</v>
       </c>
       <c r="N64" t="n">
-        <v>4.47975472831</v>
+        <v>4.484771029801355</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015161</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -3913,43 +3913,43 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.2963312576</v>
+        <v>27.33037419566903</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.293247580434</v>
+        <v>-0.3003785282004956</v>
       </c>
       <c r="E65" t="n">
-        <v>-2.36256052112</v>
+        <v>-2.350796203609318</v>
       </c>
       <c r="F65" t="n">
-        <v>1.00939866032</v>
+        <v>1.010947599141011</v>
       </c>
       <c r="G65" t="n">
-        <v>1.01061228131</v>
+        <v>1.012491309134195</v>
       </c>
       <c r="H65" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235072</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999992</v>
       </c>
       <c r="J65" t="n">
-        <v>0.119212718936</v>
+        <v>0.1192724442011758</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0132458576595</v>
+        <v>0.01325249380013064</v>
       </c>
       <c r="M65" t="n">
-        <v>0.132458576595</v>
+        <v>0.1325249380013064</v>
       </c>
       <c r="N65" t="n">
-        <v>4.47946975141</v>
+        <v>4.484468486525143</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015157</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -3967,43 +3967,43 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>27.2904427422</v>
+        <v>27.32419124793953</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.291794648877</v>
+        <v>-0.2988992558904835</v>
       </c>
       <c r="E66" t="n">
-        <v>-2.36065402313</v>
+        <v>-2.348802874456213</v>
       </c>
       <c r="F66" t="n">
-        <v>1.00915150466</v>
+        <v>1.010688951552867</v>
       </c>
       <c r="G66" t="n">
-        <v>1.01027483923</v>
+        <v>1.012137650578471</v>
       </c>
       <c r="H66" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235017</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999791</v>
       </c>
       <c r="J66" t="n">
-        <v>0.11905953456</v>
+        <v>0.1191011395930583</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0132288371734</v>
+        <v>0.01323345995478426</v>
       </c>
       <c r="M66" t="n">
-        <v>0.132288371734</v>
+        <v>0.1323345995478425</v>
       </c>
       <c r="N66" t="n">
-        <v>4.47879709063</v>
+        <v>4.483752052227847</v>
       </c>
       <c r="O66" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015211</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -4021,46 +4021,46 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>27.2357043327</v>
+        <v>27.22957061039556</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.30274063755</v>
+        <v>-0.2992956319744944</v>
       </c>
       <c r="E67" t="n">
-        <v>-2.38632781473</v>
+        <v>-2.361367092867095</v>
       </c>
       <c r="F67" t="n">
-        <v>1.01251770695</v>
+        <v>1.012289852821915</v>
       </c>
       <c r="G67" t="n">
-        <v>1.01485133101</v>
+        <v>1.014363762686251</v>
       </c>
       <c r="H67" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235068</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999979</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="N67" t="n">
-        <v>4.49065923661</v>
+        <v>4.49070367090788</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.723817579401516</v>
       </c>
       <c r="P67" t="n">
-        <v>3.61771539492</v>
+        <v>3.594248886224392</v>
       </c>
     </row>
     <row r="68">
@@ -4075,19 +4075,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F68" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G68" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4108,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O68" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -4129,43 +4129,43 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>27.3192550778</v>
+        <v>27.35432873123547</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.292207907821</v>
+        <v>-0.2994227901914837</v>
       </c>
       <c r="E69" t="n">
-        <v>-2.3694943312</v>
+        <v>-2.358030379390585</v>
       </c>
       <c r="F69" t="n">
-        <v>1.010261273</v>
+        <v>1.011850482021188</v>
       </c>
       <c r="G69" t="n">
-        <v>1.01183220116</v>
+        <v>1.013767662456683</v>
       </c>
       <c r="H69" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235086</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000046</v>
       </c>
       <c r="J69" t="n">
-        <v>0.13067475456</v>
+        <v>0.1308130416233192</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00404148725444</v>
+        <v>0.00404576417391709</v>
       </c>
       <c r="M69" t="n">
-        <v>0.134716241815</v>
+        <v>0.1348588057972363</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4835372251</v>
+        <v>4.488694381376724</v>
       </c>
       <c r="O69" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015143</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -4183,43 +4183,43 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>27.3165681752</v>
+        <v>27.3515094593545</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.291574323254</v>
+        <v>-0.2987773361852408</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.3686315681</v>
+        <v>-2.35712896388609</v>
       </c>
       <c r="F70" t="n">
-        <v>1.01014831691</v>
+        <v>1.011732354363258</v>
       </c>
       <c r="G70" t="n">
-        <v>1.01167874197</v>
+        <v>1.013606917898234</v>
       </c>
       <c r="H70" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235124</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000185</v>
       </c>
       <c r="J70" t="n">
-        <v>0.130590949742</v>
+        <v>0.130720359967911</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0.00403889535285</v>
+        <v>0.004042897730966321</v>
       </c>
       <c r="M70" t="n">
-        <v>0.134629845095</v>
+        <v>0.1347632576988774</v>
       </c>
       <c r="N70" t="n">
-        <v>4.48322234683</v>
+        <v>4.488359744106436</v>
       </c>
       <c r="O70" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015105</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -4237,43 +4237,43 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27.3100859976</v>
+        <v>27.34469662936363</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.289982265443</v>
+        <v>-0.2971554835022316</v>
       </c>
       <c r="E71" t="n">
-        <v>-2.36653982448</v>
+        <v>-2.354940181581489</v>
       </c>
       <c r="F71" t="n">
-        <v>1.00987641488</v>
+        <v>1.011447545258281</v>
       </c>
       <c r="G71" t="n">
-        <v>1.01130742531</v>
+        <v>1.013217391217531</v>
       </c>
       <c r="H71" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235151</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000283</v>
       </c>
       <c r="J71" t="n">
-        <v>0.130406560957</v>
+        <v>0.1305140034115257</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.00403319260691</v>
+        <v>0.004036515569428632</v>
       </c>
       <c r="M71" t="n">
-        <v>0.134439753564</v>
+        <v>0.1345505189809544</v>
       </c>
       <c r="N71" t="n">
-        <v>4.48247962461</v>
+        <v>4.487567842487854</v>
       </c>
       <c r="O71" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015078</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.1883443175</v>
+        <v>27.21644169598124</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.291697834652</v>
+        <v>-0.2963239746832436</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.36761019772</v>
+        <v>-2.356181093603849</v>
       </c>
       <c r="F72" t="n">
-        <v>1.01197954223</v>
+        <v>1.012148606423345</v>
       </c>
       <c r="G72" t="n">
-        <v>1.01203875577</v>
+        <v>1.013583954180803</v>
       </c>
       <c r="H72" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235074</v>
       </c>
       <c r="I72" t="n">
         <v>0.5</v>
@@ -4315,22 +4315,22 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.13712941226</v>
+        <v>0.1359331458265537</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.13712941226</v>
+        <v>0.1359331458265537</v>
       </c>
       <c r="N72" t="n">
-        <v>4.48656315468</v>
+        <v>4.48958007759303</v>
       </c>
       <c r="O72" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015155</v>
       </c>
       <c r="P72" t="n">
-        <v>21.867846839</v>
+        <v>24.61049679493723</v>
       </c>
     </row>
     <row r="73">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>27.5538992985</v>
+        <v>27.56504518468649</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.5526368095949999</v>
+        <v>-0.551670436972751</v>
       </c>
       <c r="E73" t="n">
-        <v>0.644628255699</v>
+        <v>0.653457746197339</v>
       </c>
       <c r="F73" t="n">
-        <v>0.977513343473</v>
+        <v>0.9776746282078754</v>
       </c>
       <c r="G73" t="n">
-        <v>1.02268036047</v>
+        <v>1.023270132258421</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4378,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.55050104447</v>
+        <v>4.552530806140384</v>
       </c>
       <c r="O73" t="n">
-        <v>0.937102569726</v>
+        <v>0.9383158980184443</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -4399,43 +4399,43 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>27.5918283741</v>
+        <v>27.60495556014316</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.568667784014</v>
+        <v>-0.5678466612713096</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8018664250300001</v>
+        <v>-0.793164754510145</v>
       </c>
       <c r="F74" t="n">
-        <v>0.978211423486</v>
+        <v>0.9784341369808889</v>
       </c>
       <c r="G74" t="n">
-        <v>1.02497878251</v>
+        <v>1.025677279771809</v>
       </c>
       <c r="H74" t="n">
-        <v>0.135457345323</v>
+        <v>0.1354573453235047</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999902</v>
       </c>
       <c r="J74" t="n">
-        <v>0.130627045201</v>
+        <v>0.1307685574409933</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.00404001170725</v>
+        <v>0.004044388374463709</v>
       </c>
       <c r="M74" t="n">
-        <v>0.134667056908</v>
+        <v>0.134812945815457</v>
       </c>
       <c r="N74" t="n">
-        <v>4.55290332506</v>
+        <v>4.555233813070995</v>
       </c>
       <c r="O74" t="n">
-        <v>0.801645224402</v>
+        <v>0.8028585526949396</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -4453,43 +4453,43 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>27.5890010085</v>
+        <v>27.60200253029364</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.568052871971</v>
+        <v>-0.567223754866264</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.8008646605</v>
+        <v>-0.7921206769279321</v>
       </c>
       <c r="F75" t="n">
-        <v>0.978102893807</v>
+        <v>0.9783209782160351</v>
       </c>
       <c r="G75" t="n">
-        <v>1.02481745838</v>
+        <v>1.025509078365216</v>
       </c>
       <c r="H75" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235102</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000102</v>
       </c>
       <c r="J75" t="n">
-        <v>0.130530887357</v>
+        <v>0.1306632499410314</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0040370377533</v>
+        <v>0.004041131441475197</v>
       </c>
       <c r="M75" t="n">
-        <v>0.13456792511</v>
+        <v>0.1347043813825066</v>
       </c>
       <c r="N75" t="n">
-        <v>4.55256955269</v>
+        <v>4.554880678610885</v>
       </c>
       <c r="O75" t="n">
-        <v>0.801645224402</v>
+        <v>0.8028585526949341</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -4507,43 +4507,43 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>27.5821757514</v>
+        <v>27.59487176803873</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.566512935171</v>
+        <v>-0.5656645314106479</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.798437939403</v>
+        <v>-0.7895909576203564</v>
       </c>
       <c r="F76" t="n">
-        <v>0.977840644018</v>
+        <v>0.9780474843771482</v>
       </c>
       <c r="G76" t="n">
-        <v>1.02442687072</v>
+        <v>1.025101770806867</v>
       </c>
       <c r="H76" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235057</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999938</v>
       </c>
       <c r="J76" t="n">
-        <v>0.130317625929</v>
+        <v>0.1304277560356575</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.00403044203905</v>
+        <v>0.004033848124814148</v>
       </c>
       <c r="M76" t="n">
-        <v>0.134348067968</v>
+        <v>0.1344616041604716</v>
       </c>
       <c r="N76" t="n">
-        <v>4.55178162346</v>
+        <v>4.554045684414504</v>
       </c>
       <c r="O76" t="n">
-        <v>0.801645224402</v>
+        <v>0.8028585526949386</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -4561,46 +4561,46 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>27.5115956317</v>
+        <v>27.48098878589475</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.579654107652</v>
+        <v>-0.5679528200191353</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.821675721399</v>
+        <v>-0.7971194642702684</v>
       </c>
       <c r="F77" t="n">
-        <v>0.980267749439</v>
+        <v>0.9788398196343105</v>
       </c>
       <c r="G77" t="n">
-        <v>1.02819892943</v>
+        <v>1.026318931591446</v>
       </c>
       <c r="H77" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235099</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000094</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.137748646524</v>
+        <v>0.136039587171068</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.137748646524</v>
+        <v>0.136039587171068</v>
       </c>
       <c r="N77" t="n">
-        <v>4.56064529865</v>
+        <v>4.557388589983857</v>
       </c>
       <c r="O77" t="n">
-        <v>0.801645224402</v>
+        <v>0.8028585526949343</v>
       </c>
       <c r="P77" t="n">
-        <v>3.5968888043</v>
+        <v>3.640396552556115</v>
       </c>
     </row>
     <row r="78">
@@ -4615,19 +4615,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>27.2782408461</v>
+        <v>27.31106466313496</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.275213898339</v>
+        <v>-0.2822455027838955</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.930512797475</v>
+        <v>-0.9203053886822521</v>
       </c>
       <c r="F78" t="n">
-        <v>1.00931439715</v>
+        <v>1.010819498856729</v>
       </c>
       <c r="G78" t="n">
-        <v>1.00936320039</v>
+        <v>1.011174804426402</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -4648,10 +4648,10 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.48068642993</v>
+        <v>4.485508216159974</v>
       </c>
       <c r="O78" t="n">
-        <v>0.857088751372</v>
+        <v>0.8591781856570524</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -4669,43 +4669,43 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>27.3143722192</v>
+        <v>27.34921026496464</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.290776742415</v>
+        <v>-0.2979770509368485</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.365874016</v>
+        <v>-2.354452809552854</v>
       </c>
       <c r="F79" t="n">
-        <v>1.01013707748</v>
+        <v>1.01171759287344</v>
       </c>
       <c r="G79" t="n">
-        <v>1.01154903211</v>
+        <v>1.013471570384147</v>
       </c>
       <c r="H79" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235136</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.500000000000023</v>
       </c>
       <c r="J79" t="n">
-        <v>0.130658608581</v>
+        <v>0.1307925079948641</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00404098789425</v>
+        <v>0.004045129113243219</v>
       </c>
       <c r="M79" t="n">
-        <v>0.134699596475</v>
+        <v>0.1348376371081073</v>
       </c>
       <c r="N79" t="n">
-        <v>4.48303132097</v>
+        <v>4.488152621269193</v>
       </c>
       <c r="O79" t="n">
-        <v>0.721631406048</v>
+        <v>0.7237208403335388</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -4723,43 +4723,43 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>27.3116887044</v>
+        <v>27.34639472607131</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.290144086563</v>
+        <v>-0.2973326192098114</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.36501456899</v>
+        <v>-2.353554916257716</v>
       </c>
       <c r="F80" t="n">
-        <v>1.01002422272</v>
+        <v>1.011599578426235</v>
       </c>
       <c r="G80" t="n">
-        <v>1.01139576719</v>
+        <v>1.013311039671073</v>
       </c>
       <c r="H80" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235026</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999824</v>
       </c>
       <c r="J80" t="n">
-        <v>0.130574931339</v>
+        <v>0.1306999700963327</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0.00403839993831</v>
+        <v>0.004042267116381422</v>
       </c>
       <c r="M80" t="n">
-        <v>0.134613331277</v>
+        <v>0.1347422372127141</v>
       </c>
       <c r="N80" t="n">
-        <v>4.48271682776</v>
+        <v>4.487818411570633</v>
       </c>
       <c r="O80" t="n">
-        <v>0.721631406048</v>
+        <v>0.7237208403335498</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -4777,43 +4777,43 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27.3052147344</v>
+        <v>27.33959098282492</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.2885542793</v>
+        <v>-0.2957132521442585</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.36293089073</v>
+        <v>-2.351374721808819</v>
       </c>
       <c r="F81" t="n">
-        <v>1.00975256591</v>
+        <v>1.011315044723978</v>
       </c>
       <c r="G81" t="n">
-        <v>1.01102492126</v>
+        <v>1.01292203358349</v>
       </c>
       <c r="H81" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235126</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000193</v>
       </c>
       <c r="J81" t="n">
-        <v>0.130390850258</v>
+        <v>0.1304939622575101</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.00403270670902</v>
+        <v>0.004035895739922995</v>
       </c>
       <c r="M81" t="n">
-        <v>0.134423556967</v>
+        <v>0.1345298579974331</v>
       </c>
       <c r="N81" t="n">
-        <v>4.48197503711</v>
+        <v>4.487027549869345</v>
       </c>
       <c r="O81" t="n">
-        <v>0.721631406048</v>
+        <v>0.7237208403335398</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -4831,46 +4831,46 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>27.2307798608</v>
+        <v>27.22446169245155</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.30129229946</v>
+        <v>-0.2978461399321342</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.38264517961</v>
+        <v>-2.357777063859889</v>
       </c>
       <c r="F82" t="n">
-        <v>1.01239170642</v>
+        <v>1.012156607601819</v>
       </c>
       <c r="G82" t="n">
-        <v>1.01456468319</v>
+        <v>1.01406697644401</v>
       </c>
       <c r="H82" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235086</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000046</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.137320734644</v>
+        <v>0.13595968152914</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0.137320734644</v>
+        <v>0.13595968152914</v>
       </c>
       <c r="N82" t="n">
-        <v>4.49014666649</v>
+        <v>4.490160516702039</v>
       </c>
       <c r="O82" t="n">
-        <v>0.721631406048</v>
+        <v>0.7237208403335438</v>
       </c>
       <c r="P82" t="n">
-        <v>3.61791175584</v>
+        <v>3.594448677518408</v>
       </c>
     </row>
     <row r="83">
@@ -4885,19 +4885,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>27.2818189165</v>
+        <v>27.31481464786954</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.276217828761</v>
+        <v>-0.2832595844041275</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.933063563926</v>
+        <v>-0.9227985612629164</v>
       </c>
       <c r="F83" t="n">
-        <v>1.00940882245</v>
+        <v>1.010920334297312</v>
       </c>
       <c r="G83" t="n">
-        <v>1.00957002904</v>
+        <v>1.011391053858405</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.48106754238</v>
+        <v>4.485915625391677</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8571728918730001</v>
+        <v>0.8592749247250229</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -4939,43 +4939,43 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>27.3147847099</v>
+        <v>27.34961488085379</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.290732142763</v>
+        <v>-0.2979256167855104</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.23086421102</v>
+        <v>-2.219384501541843</v>
       </c>
       <c r="F84" t="n">
-        <v>1.01014737087</v>
+        <v>1.011727467870353</v>
       </c>
       <c r="G84" t="n">
-        <v>1.01156867761</v>
+        <v>1.0134907258419</v>
       </c>
       <c r="H84" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235048</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999906</v>
       </c>
       <c r="J84" t="n">
-        <v>0.130654973861</v>
+        <v>0.1307771021087818</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.00404087548025</v>
+        <v>0.004044652642539642</v>
       </c>
       <c r="M84" t="n">
-        <v>0.134695849342</v>
+        <v>0.1348217547513214</v>
       </c>
       <c r="N84" t="n">
-        <v>4.4831401506</v>
+        <v>4.488261150536339</v>
       </c>
       <c r="O84" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.723817579401518</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -4993,43 +4993,43 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>27.3123691762</v>
+        <v>27.34708096547176</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.290162853341</v>
+        <v>-0.2973458404795681</v>
       </c>
       <c r="E85" t="n">
-        <v>-2.23015411851</v>
+        <v>-2.21864746415974</v>
       </c>
       <c r="F85" t="n">
-        <v>1.01004578151</v>
+        <v>1.01162125035808</v>
       </c>
       <c r="G85" t="n">
-        <v>1.01143072203</v>
+        <v>1.013346256443586</v>
       </c>
       <c r="H85" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235051</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999914</v>
       </c>
       <c r="J85" t="n">
-        <v>0.130579585896</v>
+        <v>0.1306937496098337</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0040385438937</v>
+        <v>0.004042074730201042</v>
       </c>
       <c r="M85" t="n">
-        <v>0.13461812979</v>
+        <v>0.1347358243400347</v>
       </c>
       <c r="N85" t="n">
-        <v>4.48285700126</v>
+        <v>4.487960304010249</v>
       </c>
       <c r="O85" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015178</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -5047,43 +5047,43 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>27.3065398326</v>
+        <v>27.34095566586537</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.288731765004</v>
+        <v>-0.2958883762838482</v>
       </c>
       <c r="E86" t="n">
-        <v>-2.22841447761</v>
+        <v>-2.21683987358956</v>
       </c>
       <c r="F86" t="n">
-        <v>1.00980117339</v>
+        <v>1.011365081405257</v>
       </c>
       <c r="G86" t="n">
-        <v>1.01109681138</v>
+        <v>1.012996050484962</v>
       </c>
       <c r="H86" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235096</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000082</v>
       </c>
       <c r="J86" t="n">
-        <v>0.130413670137</v>
+        <v>0.1305081121911727</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.00403341247846</v>
+        <v>0.004036333366737301</v>
       </c>
       <c r="M86" t="n">
-        <v>0.134447082615</v>
+        <v>0.13454444555791</v>
       </c>
       <c r="N86" t="n">
-        <v>4.48218892713</v>
+        <v>4.487248150914443</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.7238175794015133</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -5101,46 +5101,1666 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>27.2357043327</v>
+        <v>27.22957061039556</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.30274063755</v>
+        <v>-0.2992956319744944</v>
       </c>
       <c r="E87" t="n">
-        <v>-2.38632781473</v>
+        <v>-2.361367092867095</v>
       </c>
       <c r="F87" t="n">
-        <v>1.01251770695</v>
+        <v>1.012289852821915</v>
       </c>
       <c r="G87" t="n">
-        <v>1.01485133101</v>
+        <v>1.014363762686251</v>
       </c>
       <c r="H87" t="n">
-        <v>0.135457345324</v>
+        <v>0.1354573453235068</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999979</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.137339558876</v>
+        <v>0.135981353761189</v>
       </c>
       <c r="N87" t="n">
-        <v>4.49065923661</v>
+        <v>4.49070367090788</v>
       </c>
       <c r="O87" t="n">
-        <v>0.7217155465490001</v>
+        <v>0.723817579401516</v>
       </c>
       <c r="P87" t="n">
-        <v>3.61771539492</v>
+        <v>3.594248886224392</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>27.28181891652212</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.2762178289381856</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.9330635639237195</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.009408822449236</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1.009570029035069</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>4.481067542379102</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.8571728918730508</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>27.31925507781933</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-0.2922079078208073</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-2.369494331202415</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.010261273001173</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.011832201160964</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.1354573453235112</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.500000000000014</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.1306747545600716</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.004041487254435204</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.1347162418145068</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4.483537225099722</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.7217155465495396</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>27.31656817515917</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.2915743232542067</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-2.368631568101631</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.01014831690665</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1.011678741971394</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.135457345323506</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.4999999999999948</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.1305909497420594</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.004038895352847198</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.1346298450949066</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4.483222346832872</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.7217155465495448</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>27.3100859975621</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-0.2899822654425122</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-2.36653982448265</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.009876414884289</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.011307425313625</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.1354573453235104</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.5000000000000111</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.1304065609565028</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.004033192606902148</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.1344397535634049</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4.482479624607214</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.7217155465495404</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>consumption_CD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>27.23570433272043</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.3027406375533892</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-2.386327814725642</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.01251770695061</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.014851331013061</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.1354573453235068</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.4999999999999981</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.1373395588761639</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.1373395588761639</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4.490659236609885</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.721715546549544</v>
+      </c>
+      <c r="P92" t="n">
+        <v>3.617715394915096</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>27.24100916579481</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.2668863723644277</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-0.945128281887353</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.007646179400909</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.00731433545917</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>4.475124131040461</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.8546126658806408</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>27.2751296166345</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.2826488944328132</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-2.382792628054542</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.008378436132434</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.009394515571857</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1354573453235095</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.500000000000008</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.1304446072101287</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.004034369295158619</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.1344789765052873</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4.477091160611673</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7191553205571313</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>27.27265957344808</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.2820304770590476</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-2.38199415350191</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.008273996991109</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.009252946871777</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.1354573453235044</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.4999999999999892</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.1303759678497324</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.004032246428342241</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.1344082142780747</v>
+      </c>
+      <c r="N95" t="n">
+        <v>4.476809350080848</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7191553205571364</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>27.26671567226822</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.280476726377199</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-2.380062622760293</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.008023226022514</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.008911167683258</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.1354573453235035</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.4999999999999859</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.1302288154952002</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.004027695324593821</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.134256510819794</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4.476148342513038</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.7191553205571373</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>consumption_flat_CES2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>27.23980542104675</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-0.3071285206560526</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-2.415407047334539</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.01274920852919</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.015245147402333</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.1354573453235078</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.5000000000000019</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.1384701823260449</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.1384701823260449</v>
+      </c>
+      <c r="N97" t="n">
+        <v>4.489803713829089</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.7191553205571329</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3.629291521535329</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>27.30414313345949</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-0.280707491424792</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-0.9239234072323521</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.010407945433393</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.010790201129294</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>4.48453151393369</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.8587992967192739</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>27.34343744230565</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.2968203324176022</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-2.359701808025494</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.011328719022974</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.013154258205023</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.1354573453235033</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.4999999999999848</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.1308053777056606</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.004045527145535895</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.1348509048511965</v>
+      </c>
+      <c r="N99" t="n">
+        <v>4.487284504749233</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.7233419513957706</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>27.3406304491637</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.2961781571235167</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-2.358803368945595</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.011211048679608</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.01299421604703</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.1354573453235122</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.5000000000000177</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.1307131348342221</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.004042674273223363</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.1347558091074454</v>
+      </c>
+      <c r="N100" t="n">
+        <v>4.486951289188037</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7233419513957617</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>27.33384970120012</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.2945644221807653</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-2.356622559020138</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.01092743585109</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.012606519550368</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.1354573453235097</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.5000000000000087</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.130507994360946</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.004036329722503483</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.1345443240834494</v>
+      </c>
+      <c r="N101" t="n">
+        <v>4.486163180374035</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.7233419513957642</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>27.23296770860356</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.3002578021115365</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-2.367733230761937</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.012400941592223</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.014592986360586</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.1354573453235106</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.5000000000000119</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.1365335143734636</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.1365335143734636</v>
+      </c>
+      <c r="N102" t="n">
+        <v>4.491109810879625</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.7233419513957633</v>
+      </c>
+      <c r="P102" t="n">
+        <v>3.604611372893972</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>27.2893758472662</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-0.2771783390283611</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-0.925450264851968</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.009699909615118</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1.009958626510815</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>4.482617907506431</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.8581432102332989</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>27.32836709919419</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.2932217253328373</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-2.361986062884103</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.010607751704879</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1.012305375798208</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.1354573453235052</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.4999999999999919</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.1307948187858613</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.004045200581006019</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.1348400193668673</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4.485335368531003</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.7226858649097937</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>27.3255770857713</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.2925840851648598</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-2.361091744699528</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.010490714858735</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.012146304885399</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.1354573453235071</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.4999999999999989</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.1307031829590495</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.004042366483269571</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.134745549442319</v>
+      </c>
+      <c r="N105" t="n">
+        <v>4.485004120115965</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.7226858649097918</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>27.318840693536</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.2909815694996043</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-2.358921970214689</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.010208758575601</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.011761138480692</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.1354573453235135</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.5000000000000226</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.1304997258789724</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.004036073996256879</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.1345357998752293</v>
+      </c>
+      <c r="N106" t="n">
+        <v>4.484221259304932</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.7226858649097854</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>27.23785222791664</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.3016348608287256</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-2.376576213039339</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.012562571116016</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.014920902925923</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.1354573453235058</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.4999999999999943</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.1373026316381444</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.1373026316381444</v>
+      </c>
+      <c r="N107" t="n">
+        <v>4.491694828926777</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.722685864909793</v>
+      </c>
+      <c r="P107" t="n">
+        <v>3.618709934999589</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>27.31645672266057</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-0.2831730730536663</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-0.9198352371590501</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.010946948826275</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.011468448460079</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>4.486361408949863</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.8596113736904387</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>27.35673912796162</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.2993541101496855</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-2.355238757552547</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.011904011382403</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.013886724442084</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.135457345323507</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4999999999999983</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.1308743126931416</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.00404765915545799</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.1349219718485996</v>
+      </c>
+      <c r="N109" t="n">
+        <v>4.489264432572079</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.7241540283669318</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>27.35386880215928</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.298707305549395</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-2.354321674398852</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.011783859009898</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.013723209375369</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.135457345323506</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.4999999999999946</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.1307776310973487</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.004044669003010786</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.1348223001003595</v>
+      </c>
+      <c r="N110" t="n">
+        <v>4.488921565229577</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.7241540283669328</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>27.34693054354006</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.2970819342998254</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-2.352094304851937</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.011494076937846</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.013326869995125</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.1354573453235053</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.4999999999999922</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.1305615501940338</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.004037986088475273</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.1345995362825091</v>
+      </c>
+      <c r="N111" t="n">
+        <v>4.488109539132505</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.7241540283669334</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>low_within_substitution</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>27.23208466977694</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-0.2992252601760836</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-2.358630916869753</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.012350659389382</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.014492672798785</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.1354573453235071</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.4999999999999988</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.1360621917755187</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.1360621917755187</v>
+      </c>
+      <c r="N112" t="n">
+        <v>4.491305999905891</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.7241540283669317</v>
+      </c>
+      <c r="P112" t="n">
+        <v>3.595852050799183</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>27.31165023610891</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-0.2834187133579635</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-0.9285735062107725</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.010870991785117</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.011242253279837</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>4.485051229701043</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.8586203961633463</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>perfect_targeting</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>27.34970075485254</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.2995480945671702</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-2.363478850130118</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.011750059974584</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.013539487784254</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.1354573453235101</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.5000000000000099</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.1306963430772457</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.004042154940533373</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.1347384980177791</v>
+      </c>
+      <c r="N114" t="n">
+        <v>4.487593309380911</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.7231630508398362</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>pmt</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>27.34697880530348</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-0.2989051985167412</v>
+      </c>
+      <c r="E115" t="n">
+        <v>-2.362607305017972</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.011635793595304</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.013384025055693</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.1354573453235055</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.4999999999999931</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.1306112768208409</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.004039524025386832</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.1346508008462277</v>
+      </c>
+      <c r="N115" t="n">
+        <v>4.48727435300175</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.7231630508398408</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>universal_cash</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>27.34040501769698</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-0.2972900318905292</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-2.360492068464504</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.011360466792151</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.013007483573064</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1354573453235001</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.4999999999999731</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.1304234248101438</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.004033714169385891</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.1344571389795297</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4.486520781078602</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.7231630508398462</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>price_support</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>27.22474520628439</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-0.2994247714205756</v>
+      </c>
+      <c r="E117" t="n">
+        <v>-2.366709992191851</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.012175547864501</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.014116832144424</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.135457345323506</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4999999999999948</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.1358271454818568</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.1358271454818568</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4.489540873074455</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.7231630508398403</v>
+      </c>
+      <c r="P117" t="n">
+        <v>3.59120425104729</v>
       </c>
     </row>
   </sheetData>
@@ -5154,7 +6774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5992,70 +7612,142 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Policy: baseline</t>
+          <t>Scenario: consumption_CD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Unshocked benchmark equilibrium, without the new support programme.</t>
+          <t>Cobb-Douglas consumption (elasticity 1) in both CGE and microsimulation; all other main settings unchanged.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Policy: shock</t>
+          <t>Scenario: consumption_flat_CES2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>No-policy reference equilibrium under the external price shock specified by case.</t>
+          <t>Single-level CES consumption with elasticity 2 in CGE and microsimulation.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Policy: perfect_targeting</t>
+          <t>Scenario: upper_substitution_050</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+          <t>Food-energy-other upper-nest elasticity is 0.50; within-nest elasticities retain their main values.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Policy: pmt</t>
+          <t>Scenario: upper_substitution_085</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+          <t>Food-energy-other upper-nest elasticity is 0.85; within-nest elasticities retain their main values.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Policy: universal_cash</t>
+          <t>Scenario: low_within_substitution</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Universal cash: equal per-person payment to every represented person.</t>
+          <t>Within-nest elasticities are food 0.25, energy 0.20 and other 0.25; upper-nest elasticity remains 0.25.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Scenario: high_within_substitution</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Within-nest elasticities are food 1.00, energy 0.80 and other 1.00; upper-nest elasticity remains 0.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Policy: baseline</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unshocked benchmark equilibrium, without the new support programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Policy: shock</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>No-policy reference equilibrium under the external price shock specified by case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Policy: perfect_targeting</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Policy: pmt</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Policy: universal_cash</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Universal cash: equal per-person payment to every represented person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Policy: price_support</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Price support: a common proportional discount on eligible household purchases, solved at the same final net fiscal cost.</t>
         </is>
